--- a/DIJES TOUS.xlsx
+++ b/DIJES TOUS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8CE73CEF-13A0-4F78-B3E6-DCE2D3FE4E0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA48FA5-F47C-42A0-A8E5-2BF2C526AEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B3FA6899-1EB6-4006-9880-D15E10626D0C}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
   <si>
     <t>PESO GR</t>
   </si>
@@ -85,6 +85,24 @@
   </si>
   <si>
     <t>DIJES</t>
+  </si>
+  <si>
+    <t>2 - 11MM</t>
+  </si>
+  <si>
+    <t>11MM</t>
+  </si>
+  <si>
+    <t>3 - 16MM</t>
+  </si>
+  <si>
+    <t>4 - 11MM</t>
+  </si>
+  <si>
+    <t>5 - 16MM</t>
+  </si>
+  <si>
+    <t>6 - 11MM</t>
   </si>
 </sst>
 </file>
@@ -305,13 +323,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>293688</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>119063</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1031782</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>8</xdr:row>
       <xdr:rowOff>1158876</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -336,6 +354,225 @@
         <a:xfrm>
           <a:off x="2071688" y="912813"/>
           <a:ext cx="738094" cy="1039813"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>277813</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1127125</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1158512</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Imagen 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AD549367-226A-5AAE-B1FC-7D8F28394376}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2055813" y="841375"/>
+          <a:ext cx="849312" cy="1110887"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>254001</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>103187</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1047751</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1234703</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="Imagen 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CFC7F01C-83B2-C4E3-7261-E9FB45B4AB77}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2032001" y="896937"/>
+          <a:ext cx="793750" cy="1131516"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>246062</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>79376</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1023937</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1262028</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="8" name="Imagen 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96436762-91B5-560B-23BC-1ED4B82509B4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2024062" y="873126"/>
+          <a:ext cx="777875" cy="1182652"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>325438</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>71438</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1037701</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1214438</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="10" name="Imagen 9">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{49A512C0-DF85-3ADE-6CF6-FBDC7B71512E}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2103438" y="865188"/>
+          <a:ext cx="712263" cy="1143000"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>214313</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1095375</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1212917</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="13" name="Imagen 12">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{664A57C8-D0FF-014A-50C1-FE92B4C798A4}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
+        <a:srcRect t="8741"/>
+        <a:stretch/>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1992313" y="889000"/>
+          <a:ext cx="881062" cy="1117667"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -644,7 +881,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1490B05F-E857-41C2-9DD2-558A322E13CF}">
-  <dimension ref="A2:F741"/>
+  <dimension ref="A2:F746"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -688,27 +925,112 @@
     </row>
     <row r="4" spans="1:6" ht="99.75" customHeight="1">
       <c r="A4" s="2" t="s">
-        <v>7</v>
+        <v>14</v>
       </c>
       <c r="B4" s="3">
         <v>10</v>
       </c>
       <c r="C4" s="10"/>
       <c r="D4" s="9">
+        <v>6.58</v>
+      </c>
+      <c r="E4" s="4">
+        <v>155</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="99.75" customHeight="1">
+      <c r="A5" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="3">
+        <v>10</v>
+      </c>
+      <c r="C5" s="10"/>
+      <c r="D5" s="9">
         <v>6.13</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E5" s="4">
         <v>145</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F5" s="5" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="6" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="7" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="8" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="9" spans="1:6" ht="15.75" customHeight="1"/>
+    <row r="6" spans="1:6" ht="99.75" customHeight="1">
+      <c r="A6" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="3">
+        <v>10</v>
+      </c>
+      <c r="C6" s="10"/>
+      <c r="D6" s="9">
+        <v>6.58</v>
+      </c>
+      <c r="E6" s="4">
+        <v>155</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="99.75" customHeight="1">
+      <c r="A7" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B7" s="3">
+        <v>10</v>
+      </c>
+      <c r="C7" s="10"/>
+      <c r="D7" s="9">
+        <v>6.13</v>
+      </c>
+      <c r="E7" s="4">
+        <v>145</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" ht="99.75" customHeight="1">
+      <c r="A8" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B8" s="3">
+        <v>10</v>
+      </c>
+      <c r="C8" s="10"/>
+      <c r="D8" s="9">
+        <v>6.58</v>
+      </c>
+      <c r="E8" s="4">
+        <v>155</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="99.75" customHeight="1">
+      <c r="A9" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B9" s="3">
+        <v>10</v>
+      </c>
+      <c r="C9" s="10"/>
+      <c r="D9" s="9">
+        <v>6.13</v>
+      </c>
+      <c r="E9" s="4">
+        <v>145</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>6</v>
+      </c>
+    </row>
     <row r="10" spans="1:6" ht="15.75" customHeight="1"/>
     <row r="11" spans="1:6" ht="15.75" customHeight="1"/>
     <row r="12" spans="1:6" ht="15.75" customHeight="1"/>
@@ -1441,19 +1763,29 @@
     <row r="739" ht="15.75" customHeight="1"/>
     <row r="740" ht="15.75" customHeight="1"/>
     <row r="741" ht="15.75" customHeight="1"/>
+    <row r="742" ht="15.75" customHeight="1"/>
+    <row r="743" ht="15.75" customHeight="1"/>
+    <row r="744" ht="15.75" customHeight="1"/>
+    <row r="745" ht="15.75" customHeight="1"/>
+    <row r="746" ht="15.75" customHeight="1"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A4:F4">
-    <sortCondition descending="1" ref="A4"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:F9">
+    <sortCondition descending="1" ref="A9"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D4" r:id="rId1" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
+    <hyperlink ref="D9" r:id="rId1" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
+    <hyperlink ref="D8" r:id="rId2" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{919D107B-E5F1-4EC8-802B-7797BA9741B4}"/>
+    <hyperlink ref="D7" r:id="rId3" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{24C6BF2B-A90D-4DB6-A18B-EB8755744356}"/>
+    <hyperlink ref="D6" r:id="rId4" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{0A36E31A-7048-4CC5-A447-F702AFA7B183}"/>
+    <hyperlink ref="D5" r:id="rId5" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{412FABF1-9E12-4CAE-868F-144E00C4A97A}"/>
+    <hyperlink ref="D4" r:id="rId6" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{B9794C37-A52D-4EAE-A6B9-9FA098A1971C}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
-  <drawing r:id="rId3"/>
+  <pageSetup orientation="portrait" r:id="rId7"/>
+  <drawing r:id="rId8"/>
 </worksheet>
 </file>
--- a/DIJES TOUS.xlsx
+++ b/DIJES TOUS.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Usuario\Desktop\CATALOGO\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CBA48FA5-F47C-42A0-A8E5-2BF2C526AEA3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFE38934-DAC4-45F6-ABD5-5FCF4A85EE0D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{B3FA6899-1EB6-4006-9880-D15E10626D0C}"/>
   </bookViews>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="22">
   <si>
     <t>PESO GR</t>
   </si>
@@ -75,12 +75,6 @@
     <t>PRECIO</t>
   </si>
   <si>
-    <t>TAMAÑO</t>
-  </si>
-  <si>
-    <t>16MM</t>
-  </si>
-  <si>
     <t>1 - 16MM</t>
   </si>
   <si>
@@ -88,9 +82,6 @@
   </si>
   <si>
     <t>2 - 11MM</t>
-  </si>
-  <si>
-    <t>11MM</t>
   </si>
   <si>
     <t>3 - 16MM</t>
@@ -103,6 +94,36 @@
   </si>
   <si>
     <t>6 - 11MM</t>
+  </si>
+  <si>
+    <t>7- 11MM - Sodalita</t>
+  </si>
+  <si>
+    <t>8 - 11MM - Ojo de Tigre</t>
+  </si>
+  <si>
+    <t>9 - 11MM - Amatista</t>
+  </si>
+  <si>
+    <t>10 - 11MM - Cuarzo</t>
+  </si>
+  <si>
+    <t>11 - 11MM - Malaquita</t>
+  </si>
+  <si>
+    <t>12 - 16MM - TousXLea Colombo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13 - 16MM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">14 - 11MM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">15 - 16MM </t>
+  </si>
+  <si>
+    <t xml:space="preserve">16 - 16MM </t>
   </si>
 </sst>
 </file>
@@ -260,9 +281,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -272,22 +292,19 @@
     <xf numFmtId="165" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -323,13 +340,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>293688</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>119063</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1031782</xdr:colOff>
-      <xdr:row>8</xdr:row>
+      <xdr:row>18</xdr:row>
       <xdr:rowOff>1158876</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -366,13 +383,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>277813</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>47625</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1127125</xdr:colOff>
-      <xdr:row>7</xdr:row>
+      <xdr:row>17</xdr:row>
       <xdr:rowOff>1158512</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -410,13 +427,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>254001</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>103187</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1047751</xdr:colOff>
-      <xdr:row>6</xdr:row>
+      <xdr:row>16</xdr:row>
       <xdr:rowOff>1234703</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -454,13 +471,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>246062</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>79376</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1023937</xdr:colOff>
-      <xdr:row>5</xdr:row>
+      <xdr:row>15</xdr:row>
       <xdr:rowOff>1262028</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -498,13 +515,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>325438</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>71438</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1037701</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>14</xdr:row>
       <xdr:rowOff>1214438</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -542,13 +559,13 @@
     <xdr:from>
       <xdr:col>2</xdr:col>
       <xdr:colOff>214313</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>2</xdr:col>
       <xdr:colOff>1095375</xdr:colOff>
-      <xdr:row>3</xdr:row>
+      <xdr:row>13</xdr:row>
       <xdr:rowOff>1212917</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
@@ -573,6 +590,446 @@
         <a:xfrm>
           <a:off x="1992313" y="889000"/>
           <a:ext cx="881062" cy="1117667"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>174625</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1111250</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>1194612</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="Imagen 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{664505C7-DBB5-5797-68B1-A25A9F6098DD}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1952625" y="873125"/>
+          <a:ext cx="936625" cy="1115237"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>214312</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>55563</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1000125</xdr:colOff>
+      <xdr:row>11</xdr:row>
+      <xdr:rowOff>1167650</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="5" name="Imagen 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F0E8ECCC-7269-9EC6-008B-E60E273DD111}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId8"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1992312" y="849313"/>
+          <a:ext cx="785813" cy="1112087"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>277812</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>87312</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1016000</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>1183802</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="7" name="Imagen 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3DBA389C-63B2-7828-63B6-F696142DD1DB}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId9"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2055812" y="881062"/>
+          <a:ext cx="738188" cy="1096490"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>230187</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>55562</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1093920</xdr:colOff>
+      <xdr:row>9</xdr:row>
+      <xdr:rowOff>1190625</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="15" name="Imagen 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2BD029E3-CD33-AEA2-32CC-7DD60C374155}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId10"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2008187" y="849312"/>
+          <a:ext cx="863733" cy="1135063"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>222251</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>87313</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1079501</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>1197278</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="17" name="Imagen 16">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4BC10F12-CDD9-05A6-2FF1-23F1B2135E64}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId11"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2000251" y="881063"/>
+          <a:ext cx="857250" cy="1109965"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>309562</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>55563</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>992187</xdr:colOff>
+      <xdr:row>7</xdr:row>
+      <xdr:rowOff>1164829</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="9" name="Imagen 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6ABB33EC-6942-C11B-6404-86E6EBE36860}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2087562" y="849313"/>
+          <a:ext cx="682625" cy="1109266"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>293687</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>79375</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1016000</xdr:colOff>
+      <xdr:row>6</xdr:row>
+      <xdr:rowOff>1129762</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="11" name="Imagen 10">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{71E10DC5-897E-B1E2-E831-2EA07F456C50}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId13"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2071687" y="873125"/>
+          <a:ext cx="722313" cy="1050387"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>222250</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>103188</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1127125</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>1178679</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="12" name="Imagen 11">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D4E32D8E-4D17-2BD3-2780-86DFF8ACE685}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId14"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="2000250" y="896938"/>
+          <a:ext cx="904875" cy="1075491"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>174625</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>111125</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1150938</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>1163624</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="20" name="Imagen 19">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5E50AF42-7A90-D30D-A72B-DA7B22D28702}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId15"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1952625" y="904875"/>
+          <a:ext cx="976313" cy="1052499"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>134938</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>47625</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>1143001</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>1187696</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="22" name="Imagen 21">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{016D70C1-AEB9-234C-E864-4A3F2C3CAEBF}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId16"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1912938" y="841375"/>
+          <a:ext cx="1008063" cy="1140071"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -881,7 +1338,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1490B05F-E857-41C2-9DD2-558A322E13CF}">
-  <dimension ref="A2:F746"/>
+  <dimension ref="A2:E756"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="15.28515625" customWidth="1"/>
@@ -889,171 +1346,288 @@
     <col min="3" max="3" width="21" customWidth="1"/>
     <col min="4" max="4" width="13.7109375" customWidth="1"/>
     <col min="5" max="5" width="18" customWidth="1"/>
-    <col min="6" max="6" width="19.28515625" customWidth="1"/>
-    <col min="7" max="18" width="10.7109375" customWidth="1"/>
+    <col min="6" max="17" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:6" ht="28.5">
-      <c r="A2" s="11" t="s">
+    <row r="2" spans="1:5" ht="28.5">
+      <c r="A2" s="9" t="s">
+        <v>6</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="10"/>
+      <c r="D2" s="10"/>
+      <c r="E2" s="10"/>
+    </row>
+    <row r="3" spans="1:5" ht="18.75">
+      <c r="A3" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A4" s="8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B4" s="2">
+        <v>10</v>
+      </c>
+      <c r="C4" s="7"/>
+      <c r="D4" s="6">
+        <v>6.43</v>
+      </c>
+      <c r="E4" s="3">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A5" s="8" t="s">
+        <v>20</v>
+      </c>
+      <c r="B5" s="2">
+        <v>10</v>
+      </c>
+      <c r="C5" s="7"/>
+      <c r="D5" s="6">
+        <v>6.88</v>
+      </c>
+      <c r="E5" s="3">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A6" s="8" t="s">
+        <v>19</v>
+      </c>
+      <c r="B6" s="2">
+        <v>10</v>
+      </c>
+      <c r="C6" s="7"/>
+      <c r="D6" s="6">
+        <v>7.48</v>
+      </c>
+      <c r="E6" s="3">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A7" s="8" t="s">
+        <v>18</v>
+      </c>
+      <c r="B7" s="2">
+        <v>10</v>
+      </c>
+      <c r="C7" s="7"/>
+      <c r="D7" s="6">
+        <v>11.96</v>
+      </c>
+      <c r="E7" s="3">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A8" s="8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" s="2">
+        <v>10</v>
+      </c>
+      <c r="C8" s="7"/>
+      <c r="D8" s="6">
+        <v>8.9700000000000006</v>
+      </c>
+      <c r="E8" s="3">
+        <v>195</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A9" s="8" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="2">
+        <v>10</v>
+      </c>
+      <c r="C9" s="7"/>
+      <c r="D9" s="6">
+        <v>6.58</v>
+      </c>
+      <c r="E9" s="3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A10" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="B10" s="2">
+        <v>10</v>
+      </c>
+      <c r="C10" s="7"/>
+      <c r="D10" s="6">
+        <v>6.58</v>
+      </c>
+      <c r="E10" s="3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A11" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="B11" s="2">
+        <v>10</v>
+      </c>
+      <c r="C11" s="7"/>
+      <c r="D11" s="6">
+        <v>6.58</v>
+      </c>
+      <c r="E11" s="3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A12" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="2">
+        <v>10</v>
+      </c>
+      <c r="C12" s="7"/>
+      <c r="D12" s="6">
+        <v>6.58</v>
+      </c>
+      <c r="E12" s="3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A13" s="8" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="2">
+        <v>10</v>
+      </c>
+      <c r="C13" s="7"/>
+      <c r="D13" s="6">
+        <v>6.58</v>
+      </c>
+      <c r="E13" s="3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A14" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="B14" s="2">
+        <v>10</v>
+      </c>
+      <c r="C14" s="7"/>
+      <c r="D14" s="6">
+        <v>6.58</v>
+      </c>
+      <c r="E14" s="3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A15" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B15" s="2">
+        <v>10</v>
+      </c>
+      <c r="C15" s="7"/>
+      <c r="D15" s="6">
+        <v>6.13</v>
+      </c>
+      <c r="E15" s="3">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A16" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="B16" s="2">
+        <v>10</v>
+      </c>
+      <c r="C16" s="7"/>
+      <c r="D16" s="6">
+        <v>6.58</v>
+      </c>
+      <c r="E16" s="3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A17" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="B2" s="12"/>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="1"/>
+      <c r="B17" s="2">
+        <v>10</v>
+      </c>
+      <c r="C17" s="7"/>
+      <c r="D17" s="6">
+        <v>6.13</v>
+      </c>
+      <c r="E17" s="3">
+        <v>145</v>
+      </c>
     </row>
-    <row r="3" spans="1:6" ht="18.75">
-      <c r="A3" s="6" t="s">
-        <v>3</v>
-      </c>
-      <c r="B3" s="6" t="s">
-        <v>0</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>1</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>4</v>
-      </c>
-      <c r="F3" s="8" t="s">
+    <row r="18" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A18" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B18" s="2">
+        <v>10</v>
+      </c>
+      <c r="C18" s="7"/>
+      <c r="D18" s="6">
+        <v>6.58</v>
+      </c>
+      <c r="E18" s="3">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" ht="99.75" customHeight="1">
+      <c r="A19" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B19" s="2">
+        <v>10</v>
+      </c>
+      <c r="C19" s="7"/>
+      <c r="D19" s="6">
+        <v>6.13</v>
+      </c>
+      <c r="E19" s="3">
+        <v>145</v>
+      </c>
     </row>
-    <row r="4" spans="1:6" ht="99.75" customHeight="1">
-      <c r="A4" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="B4" s="3">
-        <v>10</v>
-      </c>
-      <c r="C4" s="10"/>
-      <c r="D4" s="9">
-        <v>6.58</v>
-      </c>
-      <c r="E4" s="4">
-        <v>155</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6" ht="99.75" customHeight="1">
-      <c r="A5" s="2" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="3">
-        <v>10</v>
-      </c>
-      <c r="C5" s="10"/>
-      <c r="D5" s="9">
-        <v>6.13</v>
-      </c>
-      <c r="E5" s="4">
-        <v>145</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" ht="99.75" customHeight="1">
-      <c r="A6" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6" s="3">
-        <v>10</v>
-      </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="9">
-        <v>6.58</v>
-      </c>
-      <c r="E6" s="4">
-        <v>155</v>
-      </c>
-      <c r="F6" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" ht="99.75" customHeight="1">
-      <c r="A7" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="B7" s="3">
-        <v>10</v>
-      </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="9">
-        <v>6.13</v>
-      </c>
-      <c r="E7" s="4">
-        <v>145</v>
-      </c>
-      <c r="F7" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" ht="99.75" customHeight="1">
-      <c r="A8" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="B8" s="3">
-        <v>10</v>
-      </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="9">
-        <v>6.58</v>
-      </c>
-      <c r="E8" s="4">
-        <v>155</v>
-      </c>
-      <c r="F8" s="5" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" ht="99.75" customHeight="1">
-      <c r="A9" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3">
-        <v>10</v>
-      </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="9">
-        <v>6.13</v>
-      </c>
-      <c r="E9" s="4">
-        <v>145</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="11" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="12" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="13" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="14" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="15" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="16" spans="1:6" ht="15.75" customHeight="1"/>
-    <row r="17" ht="15.75" customHeight="1"/>
-    <row r="18" ht="15.75" customHeight="1"/>
-    <row r="19" ht="15.75" customHeight="1"/>
-    <row r="20" ht="15.75" customHeight="1"/>
-    <row r="21" ht="15.75" customHeight="1"/>
-    <row r="22" ht="15.75" customHeight="1"/>
-    <row r="23" ht="15.75" customHeight="1"/>
-    <row r="24" ht="15.75" customHeight="1"/>
-    <row r="25" ht="15.75" customHeight="1"/>
-    <row r="26" ht="15.75" customHeight="1"/>
-    <row r="27" ht="15.75" customHeight="1"/>
-    <row r="28" ht="15.75" customHeight="1"/>
-    <row r="29" ht="15.75" customHeight="1"/>
-    <row r="30" ht="15.75" customHeight="1"/>
-    <row r="31" ht="15.75" customHeight="1"/>
-    <row r="32" ht="15.75" customHeight="1"/>
+    <row r="20" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="21" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="22" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="23" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="24" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="25" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="26" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="27" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="28" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="29" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="30" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="31" spans="1:5" ht="15.75" customHeight="1"/>
+    <row r="32" spans="1:5" ht="15.75" customHeight="1"/>
     <row r="33" ht="15.75" customHeight="1"/>
     <row r="34" ht="15.75" customHeight="1"/>
     <row r="35" ht="15.75" customHeight="1"/>
@@ -1768,24 +2342,44 @@
     <row r="744" ht="15.75" customHeight="1"/>
     <row r="745" ht="15.75" customHeight="1"/>
     <row r="746" ht="15.75" customHeight="1"/>
+    <row r="747" ht="15.75" customHeight="1"/>
+    <row r="748" ht="15.75" customHeight="1"/>
+    <row r="749" ht="15.75" customHeight="1"/>
+    <row r="750" ht="15.75" customHeight="1"/>
+    <row r="751" ht="15.75" customHeight="1"/>
+    <row r="752" ht="15.75" customHeight="1"/>
+    <row r="753" ht="15.75" customHeight="1"/>
+    <row r="754" ht="15.75" customHeight="1"/>
+    <row r="755" ht="15.75" customHeight="1"/>
+    <row r="756" ht="15.75" customHeight="1"/>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A9:F9">
-    <sortCondition descending="1" ref="A9"/>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A19:E19">
+    <sortCondition descending="1" ref="A19"/>
   </sortState>
   <mergeCells count="1">
     <mergeCell ref="A2:E2"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink ref="D9" r:id="rId1" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
-    <hyperlink ref="D8" r:id="rId2" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{919D107B-E5F1-4EC8-802B-7797BA9741B4}"/>
-    <hyperlink ref="D7" r:id="rId3" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{24C6BF2B-A90D-4DB6-A18B-EB8755744356}"/>
-    <hyperlink ref="D6" r:id="rId4" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{0A36E31A-7048-4CC5-A447-F702AFA7B183}"/>
-    <hyperlink ref="D5" r:id="rId5" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{412FABF1-9E12-4CAE-868F-144E00C4A97A}"/>
-    <hyperlink ref="D4" r:id="rId6" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{B9794C37-A52D-4EAE-A6B9-9FA098A1971C}"/>
+    <hyperlink ref="D19" r:id="rId1" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{7FB7C1BC-0330-425F-9AD9-7E1483AADFFE}"/>
+    <hyperlink ref="D18" r:id="rId2" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{919D107B-E5F1-4EC8-802B-7797BA9741B4}"/>
+    <hyperlink ref="D17" r:id="rId3" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{24C6BF2B-A90D-4DB6-A18B-EB8755744356}"/>
+    <hyperlink ref="D16" r:id="rId4" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{0A36E31A-7048-4CC5-A447-F702AFA7B183}"/>
+    <hyperlink ref="D15" r:id="rId5" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{412FABF1-9E12-4CAE-868F-144E00C4A97A}"/>
+    <hyperlink ref="D14" r:id="rId6" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{B9794C37-A52D-4EAE-A6B9-9FA098A1971C}"/>
+    <hyperlink ref="D13" r:id="rId7" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{AF7E039C-970C-489F-A93E-7904294F1A38}"/>
+    <hyperlink ref="D12" r:id="rId8" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{22C16A2E-A778-4325-A7F4-3657C9DC46B0}"/>
+    <hyperlink ref="D11" r:id="rId9" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{E82EBBEA-29C7-463E-8118-F0BC16CE8A00}"/>
+    <hyperlink ref="D10" r:id="rId10" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{876824BA-F34D-4C9D-9C50-C758E9ED1A97}"/>
+    <hyperlink ref="D9" r:id="rId11" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{530A311D-8019-4E03-9E57-01B8E5418F3C}"/>
+    <hyperlink ref="D8" r:id="rId12" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{9FF4B901-C19F-486F-92E8-4BC7BE727621}"/>
+    <hyperlink ref="D7" r:id="rId13" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{11FF7A8A-081A-41D0-8720-5A5A18C8F902}"/>
+    <hyperlink ref="D6" r:id="rId14" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{E1C26E5B-1BF3-41AE-A48F-05D01510353B}"/>
+    <hyperlink ref="D5" r:id="rId15" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{852BB957-80A5-4B2A-B419-FAA5221C48FF}"/>
+    <hyperlink ref="D4" r:id="rId16" display="https://detail.1688.com/offer/1086384226831.html?spm=a2615.pc_new_goods/2506.wp_pc_new_product_list.0" xr:uid="{2E1546B7-5C6C-43A8-AA51-CB29DFFB8A72}"/>
   </hyperlinks>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.70866141732283472" right="0.70866141732283472" top="0.74803149606299213" bottom="0.74803149606299213" header="0" footer="0"/>
-  <pageSetup orientation="portrait" r:id="rId7"/>
-  <drawing r:id="rId8"/>
+  <pageSetup orientation="portrait" r:id="rId17"/>
+  <drawing r:id="rId18"/>
 </worksheet>
 </file>